--- a/Figure 2/Figure 2-B.xlsx
+++ b/Figure 2/Figure 2-B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D74886-919F-4C11-958D-98650F564D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231C6D6E-1BE0-422C-99B9-56E6A7E7DE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,13 +122,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -160,7 +160,6 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -442,18 +441,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B21"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -461,7 +460,7 @@
         <v>0.31666666666666643</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -469,7 +468,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -477,7 +476,7 @@
         <v>0.36666666666666653</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -485,7 +484,7 @@
         <v>0.18333333333333299</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -493,7 +492,7 @@
         <v>0.31666666666666704</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -501,7 +500,7 @@
         <v>6.666666666666643E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -509,7 +508,7 @@
         <v>0.10000000000000024</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -517,7 +516,7 @@
         <v>0.14999999999999977</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -525,7 +524,7 @@
         <v>9.9999999999999645E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -533,7 +532,7 @@
         <v>0.19999999999999987</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -541,7 +540,7 @@
         <v>6.6666666666667027E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -549,7 +548,7 @@
         <v>0.11666666666666654</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -557,7 +556,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -565,7 +564,7 @@
         <v>0.13333333333333344</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -573,7 +572,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -581,7 +580,7 @@
         <v>0.36666666666666653</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -589,7 +588,7 @@
         <v>0.28333333333333321</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -597,7 +596,7 @@
         <v>0.23333333333333309</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -605,7 +604,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
